--- a/april2026_planning.xlsx
+++ b/april2026_planning.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\diksh\Downloads\codingal_9-12\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{130CA39C-BE70-4A5E-A901-2BA61932A684}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8997DE4-6464-41C8-80BB-B8F15F8D1801}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9ACDE515-604A-4D1A-BA1C-75C303D547D5}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="16">
   <si>
     <t>Wednesday</t>
   </si>
@@ -62,25 +62,28 @@
     <t>7:00 - 7:30</t>
   </si>
   <si>
-    <t>11:00 - 12:00</t>
-  </si>
-  <si>
-    <t>1:00 - 2:00</t>
-  </si>
-  <si>
-    <t>5:00 - 6:00</t>
-  </si>
-  <si>
-    <t>9:00 - 10:00</t>
-  </si>
-  <si>
-    <t>6:00 - 7:00</t>
-  </si>
-  <si>
     <t>Sundays</t>
   </si>
   <si>
-    <t>M-F, Saturdays</t>
+    <t>5:30 - 6:00</t>
+  </si>
+  <si>
+    <t>COURSE</t>
+  </si>
+  <si>
+    <t>TRIAL</t>
+  </si>
+  <si>
+    <t>Mon, Tues</t>
+  </si>
+  <si>
+    <t>5:30 - 6:30</t>
+  </si>
+  <si>
+    <t>Thurs, Fri, Saturday</t>
+  </si>
+  <si>
+    <t>11:00 -  4:00</t>
   </si>
 </sst>
 </file>
@@ -487,8 +490,11 @@
       <c r="C3">
         <v>2</v>
       </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
       <c r="F3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
@@ -501,6 +507,9 @@
       <c r="C4">
         <v>2</v>
       </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
@@ -510,10 +519,13 @@
         <v>3</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
       </c>
       <c r="F5" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -524,7 +536,10 @@
         <v>4</v>
       </c>
       <c r="C6">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="D6" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -535,10 +550,13 @@
         <v>5</v>
       </c>
       <c r="C7">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="D7" t="s">
+        <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -549,7 +567,10 @@
         <v>6</v>
       </c>
       <c r="C8">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="D8" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -573,6 +594,9 @@
       <c r="C10">
         <v>2</v>
       </c>
+      <c r="D10" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
@@ -584,8 +608,11 @@
       <c r="C11">
         <v>2</v>
       </c>
+      <c r="D11" t="s">
+        <v>11</v>
+      </c>
       <c r="F11" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
@@ -596,7 +623,10 @@
         <v>3</v>
       </c>
       <c r="C12">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D12" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
@@ -607,7 +637,13 @@
         <v>4</v>
       </c>
       <c r="C13">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="D13" t="s">
+        <v>10</v>
+      </c>
+      <c r="F13" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
@@ -618,7 +654,10 @@
         <v>5</v>
       </c>
       <c r="C14">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="D14" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
@@ -629,7 +668,13 @@
         <v>6</v>
       </c>
       <c r="C15">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="D15" t="s">
+        <v>10</v>
+      </c>
+      <c r="F15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
@@ -640,7 +685,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>46128</v>
       </c>
@@ -650,8 +695,11 @@
       <c r="C17">
         <v>2</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D17" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>46129</v>
       </c>
@@ -661,11 +709,11 @@
       <c r="C18">
         <v>2</v>
       </c>
-      <c r="F18" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D18" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>46130</v>
       </c>
@@ -673,10 +721,13 @@
         <v>3</v>
       </c>
       <c r="C19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+      <c r="D19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>46131</v>
       </c>
@@ -684,13 +735,13 @@
         <v>4</v>
       </c>
       <c r="C20">
-        <v>4</v>
-      </c>
-      <c r="F20" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+      <c r="D20" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>46132</v>
       </c>
@@ -698,10 +749,13 @@
         <v>5</v>
       </c>
       <c r="C21">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="D21" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>46133</v>
       </c>
@@ -709,13 +763,13 @@
         <v>6</v>
       </c>
       <c r="C22">
-        <v>2</v>
-      </c>
-      <c r="F22" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="D22" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>46134</v>
       </c>
@@ -723,7 +777,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>46135</v>
       </c>
@@ -733,8 +787,11 @@
       <c r="C24">
         <v>2</v>
       </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D24" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>46136</v>
       </c>
@@ -744,8 +801,11 @@
       <c r="C25">
         <v>2</v>
       </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D25" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>46137</v>
       </c>
@@ -753,10 +813,13 @@
         <v>3</v>
       </c>
       <c r="C26">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+      <c r="D26" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>46138</v>
       </c>
@@ -764,10 +827,13 @@
         <v>4</v>
       </c>
       <c r="C27">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+      <c r="D27" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>46139</v>
       </c>
@@ -775,10 +841,13 @@
         <v>5</v>
       </c>
       <c r="C28">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="D28" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>46140</v>
       </c>
@@ -786,10 +855,13 @@
         <v>6</v>
       </c>
       <c r="C29">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="D29" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>46141</v>
       </c>
@@ -797,7 +869,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>46142</v>
       </c>
@@ -807,8 +879,11 @@
       <c r="C31">
         <v>2</v>
       </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D31" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C32">
         <f>SUM(C2:C31)</f>
         <v>54</v>
